--- a/models/CHEMICALS.xlsx
+++ b/models/CHEMICALS.xlsx
@@ -489,7 +489,7 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>Generated 2026-10-29T07:56:59+07:00 by the coverage engine. The engine (scripts/cov_engine.py) is the source of truth; this workbook is a live rendering of it.</t>
+          <t>Generated 2026-10-29T18:55:56+07:00 by the coverage engine. The engine (scripts/cov_engine.py) is the source of truth; this workbook is a live rendering of it.</t>
         </is>
       </c>
     </row>
@@ -1017,13 +1017,13 @@
         <v/>
       </c>
       <c r="H2" s="9" t="n">
-        <v>15.295924</v>
+        <v>15.366066</v>
       </c>
       <c r="I2" s="9" t="n">
-        <v>8.647796</v>
+        <v>8.673427999999999</v>
       </c>
       <c r="J2" s="10" t="n">
-        <v>0.006538</v>
+        <v>0.006508</v>
       </c>
     </row>
   </sheetData>
@@ -4635,7 +4635,7 @@
         </is>
       </c>
       <c r="C79" s="3" t="n">
-        <v>18183</v>
+        <v>18100</v>
       </c>
     </row>
     <row r="80">
@@ -4768,7 +4768,7 @@
         </is>
       </c>
       <c r="C92" s="22" t="n">
-        <v>0.8286913296168552</v>
+        <v>0.824908599574607</v>
       </c>
     </row>
     <row r="93">
@@ -5121,7 +5121,7 @@
         </is>
       </c>
       <c r="C116" s="16" t="n">
-        <v>9.806533880662046</v>
+        <v>9.761769963151462</v>
       </c>
     </row>
     <row r="117">
@@ -5152,7 +5152,7 @@
         </is>
       </c>
       <c r="C119" s="16" t="n">
-        <v>623.0559148658679</v>
+        <v>619.9699578316099</v>
       </c>
     </row>
     <row r="120">
@@ -5182,7 +5182,7 @@
         </is>
       </c>
       <c r="C122" s="16" t="n">
-        <v>3625.894976873178</v>
+        <v>3608.245505715186</v>
       </c>
     </row>
     <row r="123">
@@ -5224,7 +5224,7 @@
         </is>
       </c>
       <c r="C126" s="19" t="n">
-        <v>0.873155</v>
+        <v>0.8773</v>
       </c>
     </row>
     <row r="127">
@@ -5365,19 +5365,19 @@
         <v>-0.01</v>
       </c>
       <c r="D140" s="25" t="n">
-        <v>1703.41159</v>
+        <v>1695.361346</v>
       </c>
       <c r="E140" s="25" t="n">
-        <v>1572.285046</v>
+        <v>1564.864291</v>
       </c>
       <c r="F140" s="25" t="n">
-        <v>1455.538127</v>
+        <v>1448.676287</v>
       </c>
       <c r="G140" s="25" t="n">
-        <v>1350.932831</v>
+        <v>1344.570543</v>
       </c>
       <c r="H140" s="25" t="n">
-        <v>1256.671832</v>
+        <v>1250.758691</v>
       </c>
     </row>
     <row r="141">
@@ -5385,19 +5385,19 @@
         <v>-0.005</v>
       </c>
       <c r="D141" s="25" t="n">
-        <v>1782.985325</v>
+        <v>1774.546156</v>
       </c>
       <c r="E141" s="25" t="n">
-        <v>1640.111728</v>
+        <v>1632.360493</v>
       </c>
       <c r="F141" s="25" t="n">
-        <v>1513.772738</v>
+        <v>1506.627941</v>
       </c>
       <c r="G141" s="25" t="n">
-        <v>1401.256735</v>
+        <v>1394.650535</v>
       </c>
       <c r="H141" s="25" t="n">
-        <v>1300.413483</v>
+        <v>1294.28881</v>
       </c>
     </row>
     <row r="142">
@@ -5405,19 +5405,19 @@
         <v>0</v>
       </c>
       <c r="D142" s="25" t="n">
-        <v>1873.657671</v>
+        <v>1864.773805</v>
       </c>
       <c r="E142" s="25" t="n">
-        <v>1716.781869</v>
+        <v>1708.655926</v>
       </c>
       <c r="F142" s="25" t="n">
-        <v>1579.13547</v>
+        <v>1571.672219</v>
       </c>
       <c r="G142" s="25" t="n">
-        <v>1457.38521</v>
+        <v>1450.506304</v>
       </c>
       <c r="H142" s="25" t="n">
-        <v>1348.92537</v>
+        <v>1342.565584</v>
       </c>
     </row>
     <row r="143">
@@ -5425,19 +5425,19 @@
         <v>0.005</v>
       </c>
       <c r="D143" s="25" t="n">
-        <v>1977.92468</v>
+        <v>1968.527433</v>
       </c>
       <c r="E143" s="25" t="n">
-        <v>1804.145639</v>
+        <v>1795.591256</v>
       </c>
       <c r="F143" s="25" t="n">
-        <v>1653.020401</v>
+        <v>1645.196079</v>
       </c>
       <c r="G143" s="25" t="n">
-        <v>1520.384007</v>
+        <v>1513.198184</v>
       </c>
       <c r="H143" s="25" t="n">
-        <v>1403.032824</v>
+        <v>1396.410168</v>
       </c>
     </row>
     <row r="144">
@@ -5445,19 +5445,19 @@
         <v>0.01</v>
       </c>
       <c r="D144" s="25" t="n">
-        <v>2099.091535</v>
+        <v>2089.094995</v>
       </c>
       <c r="E144" s="25" t="n">
-        <v>1904.608012</v>
+        <v>1895.559014</v>
       </c>
       <c r="F144" s="25" t="n">
-        <v>1737.210494</v>
+        <v>1728.973323</v>
       </c>
       <c r="G144" s="25" t="n">
-        <v>1591.596786</v>
+        <v>1584.062974</v>
       </c>
       <c r="H144" s="25" t="n">
-        <v>1463.763218</v>
+        <v>1456.844717</v>
       </c>
     </row>
     <row r="146">
@@ -5494,19 +5494,19 @@
         <v>-0.02</v>
       </c>
       <c r="D148" s="25" t="n">
-        <v>840.827341</v>
+        <v>836.6907179999999</v>
       </c>
       <c r="E148" s="25" t="n">
-        <v>1024.456511</v>
+        <v>1019.425839</v>
       </c>
       <c r="F148" s="25" t="n">
-        <v>1231.755973</v>
+        <v>1225.715582</v>
       </c>
       <c r="G148" s="25" t="n">
-        <v>1465.422545</v>
+        <v>1458.243559</v>
       </c>
       <c r="H148" s="25" t="n">
-        <v>1728.398364</v>
+        <v>1719.9375</v>
       </c>
     </row>
     <row r="149">
@@ -5514,19 +5514,19 @@
         <v>-0.01</v>
       </c>
       <c r="D149" s="25" t="n">
-        <v>1058.598767</v>
+        <v>1053.411478</v>
       </c>
       <c r="E149" s="25" t="n">
-        <v>1274.24497</v>
+        <v>1268.007963</v>
       </c>
       <c r="F149" s="25" t="n">
-        <v>1518.644807</v>
+        <v>1511.217592</v>
       </c>
       <c r="G149" s="25" t="n">
-        <v>1795.259521</v>
+        <v>1786.484662</v>
       </c>
       <c r="H149" s="25" t="n">
-        <v>2107.897687</v>
+        <v>2097.599101</v>
       </c>
     </row>
     <row r="150">
@@ -5534,19 +5534,19 @@
         <v>0</v>
       </c>
       <c r="D150" s="25" t="n">
-        <v>1276.370194</v>
+        <v>1270.132238</v>
       </c>
       <c r="E150" s="25" t="n">
-        <v>1524.033429</v>
+        <v>1516.590087</v>
       </c>
       <c r="F150" s="25" t="n">
-        <v>1805.533641</v>
+        <v>1796.719602</v>
       </c>
       <c r="G150" s="25" t="n">
-        <v>2125.096497</v>
+        <v>2114.725766</v>
       </c>
       <c r="H150" s="25" t="n">
-        <v>2487.397009</v>
+        <v>2475.260702</v>
       </c>
     </row>
     <row r="151">
@@ -5554,19 +5554,19 @@
         <v>0.01</v>
       </c>
       <c r="D151" s="25" t="n">
-        <v>1494.14162</v>
+        <v>1486.852998</v>
       </c>
       <c r="E151" s="25" t="n">
-        <v>1773.821889</v>
+        <v>1765.172211</v>
       </c>
       <c r="F151" s="25" t="n">
-        <v>2092.422475</v>
+        <v>2082.221612</v>
       </c>
       <c r="G151" s="25" t="n">
-        <v>2454.933473</v>
+        <v>2442.966869</v>
       </c>
       <c r="H151" s="25" t="n">
-        <v>2866.896332</v>
+        <v>2852.922304</v>
       </c>
     </row>
     <row r="152">
@@ -5574,19 +5574,19 @@
         <v>0.02</v>
       </c>
       <c r="D152" s="25" t="n">
-        <v>1711.913046</v>
+        <v>1703.573758</v>
       </c>
       <c r="E152" s="25" t="n">
-        <v>2023.610348</v>
+        <v>2013.754335</v>
       </c>
       <c r="F152" s="25" t="n">
-        <v>2379.311309</v>
+        <v>2367.723623</v>
       </c>
       <c r="G152" s="25" t="n">
-        <v>2784.770449</v>
+        <v>2771.207973</v>
       </c>
       <c r="H152" s="25" t="n">
-        <v>3246.395654</v>
+        <v>3230.583905</v>
       </c>
     </row>
   </sheetData>

--- a/models/CHEMICALS.xlsx
+++ b/models/CHEMICALS.xlsx
@@ -489,7 +489,7 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>Generated 2026-10-29T18:55:56+07:00 by the coverage engine. The engine (scripts/cov_engine.py) is the source of truth; this workbook is a live rendering of it.</t>
+          <t>Generated 2026-10-29T23:12:35+07:00 by the coverage engine. The engine (scripts/cov_engine.py) is the source of truth; this workbook is a live rendering of it.</t>
         </is>
       </c>
     </row>
@@ -808,7 +808,7 @@
         </is>
       </c>
       <c r="C9" s="4" t="n">
-        <v>0.05045</v>
+        <v>0.05009</v>
       </c>
       <c r="D9" s="5" t="inlineStr">
         <is>
@@ -1017,13 +1017,13 @@
         <v/>
       </c>
       <c r="H2" s="9" t="n">
-        <v>15.366066</v>
+        <v>15.344871</v>
       </c>
       <c r="I2" s="9" t="n">
-        <v>8.673427999999999</v>
+        <v>8.665683</v>
       </c>
       <c r="J2" s="10" t="n">
-        <v>0.006508</v>
+        <v>0.006517</v>
       </c>
     </row>
   </sheetData>
@@ -4635,7 +4635,7 @@
         </is>
       </c>
       <c r="C79" s="3" t="n">
-        <v>18100</v>
+        <v>18125</v>
       </c>
     </row>
     <row r="80">
@@ -4768,7 +4768,7 @@
         </is>
       </c>
       <c r="C92" s="22" t="n">
-        <v>0.824908599574607</v>
+        <v>0.8260479760933566</v>
       </c>
     </row>
     <row r="93">
@@ -5121,7 +5121,7 @@
         </is>
       </c>
       <c r="C116" s="16" t="n">
-        <v>9.761769963151462</v>
+        <v>9.775253070835372</v>
       </c>
     </row>
     <row r="117">
@@ -5152,7 +5152,7 @@
         </is>
       </c>
       <c r="C119" s="16" t="n">
-        <v>619.9699578316099</v>
+        <v>625.4777962626439</v>
       </c>
     </row>
     <row r="120">
@@ -5182,7 +5182,7 @@
         </is>
       </c>
       <c r="C122" s="16" t="n">
-        <v>3608.245505715186</v>
+        <v>3630.117672182625</v>
       </c>
     </row>
     <row r="123">
@@ -5224,7 +5224,7 @@
         </is>
       </c>
       <c r="C126" s="19" t="n">
-        <v>0.8773</v>
+        <v>0.871427</v>
       </c>
     </row>
     <row r="127">
@@ -5365,19 +5365,19 @@
         <v>-0.01</v>
       </c>
       <c r="D140" s="25" t="n">
-        <v>1695.361346</v>
+        <v>1706.816609</v>
       </c>
       <c r="E140" s="25" t="n">
-        <v>1564.864291</v>
+        <v>1575.111024</v>
       </c>
       <c r="F140" s="25" t="n">
-        <v>1448.676287</v>
+        <v>1457.898613</v>
       </c>
       <c r="G140" s="25" t="n">
-        <v>1344.570543</v>
+        <v>1352.916323</v>
       </c>
       <c r="H140" s="25" t="n">
-        <v>1250.758691</v>
+        <v>1258.348095</v>
       </c>
     </row>
     <row r="141">
@@ -5385,19 +5385,19 @@
         <v>-0.005</v>
       </c>
       <c r="D141" s="25" t="n">
-        <v>1774.546156</v>
+        <v>1786.965755</v>
       </c>
       <c r="E141" s="25" t="n">
-        <v>1632.360493</v>
+        <v>1643.394726</v>
       </c>
       <c r="F141" s="25" t="n">
-        <v>1506.627941</v>
+        <v>1516.500075</v>
       </c>
       <c r="G141" s="25" t="n">
-        <v>1394.650535</v>
+        <v>1403.537483</v>
       </c>
       <c r="H141" s="25" t="n">
-        <v>1294.28881</v>
+        <v>1302.332646</v>
       </c>
     </row>
     <row r="142">
@@ -5405,19 +5405,19 @@
         <v>0</v>
       </c>
       <c r="D142" s="25" t="n">
-        <v>1864.773805</v>
+        <v>1878.343454</v>
       </c>
       <c r="E142" s="25" t="n">
-        <v>1708.655926</v>
+        <v>1720.618452</v>
       </c>
       <c r="F142" s="25" t="n">
-        <v>1571.672219</v>
+        <v>1582.302524</v>
       </c>
       <c r="G142" s="25" t="n">
-        <v>1450.506304</v>
+        <v>1460.018946</v>
       </c>
       <c r="H142" s="25" t="n">
-        <v>1342.565584</v>
+        <v>1351.130577</v>
       </c>
     </row>
     <row r="143">
@@ -5425,19 +5425,19 @@
         <v>0.005</v>
       </c>
       <c r="D143" s="25" t="n">
-        <v>1968.527433</v>
+        <v>1983.487049</v>
       </c>
       <c r="E143" s="25" t="n">
-        <v>1795.591256</v>
+        <v>1808.660893</v>
       </c>
       <c r="F143" s="25" t="n">
-        <v>1645.196079</v>
+        <v>1656.72014</v>
       </c>
       <c r="G143" s="25" t="n">
-        <v>1513.198184</v>
+        <v>1523.440888</v>
       </c>
       <c r="H143" s="25" t="n">
-        <v>1396.410168</v>
+        <v>1405.577739</v>
       </c>
     </row>
     <row r="144">
@@ -5445,19 +5445,19 @@
         <v>0.01</v>
       </c>
       <c r="D144" s="25" t="n">
-        <v>2089.094995</v>
+        <v>2105.760652</v>
       </c>
       <c r="E144" s="25" t="n">
-        <v>1895.559014</v>
+        <v>1909.966778</v>
       </c>
       <c r="F144" s="25" t="n">
-        <v>1728.973323</v>
+        <v>1741.563346</v>
       </c>
       <c r="G144" s="25" t="n">
-        <v>1584.062974</v>
+        <v>1595.166331</v>
       </c>
       <c r="H144" s="25" t="n">
-        <v>1456.844717</v>
+        <v>1466.715405</v>
       </c>
     </row>
     <row r="146">
@@ -5494,19 +5494,19 @@
         <v>-0.02</v>
       </c>
       <c r="D148" s="25" t="n">
-        <v>836.6907179999999</v>
+        <v>843.198402</v>
       </c>
       <c r="E148" s="25" t="n">
-        <v>1019.425839</v>
+        <v>1027.051685</v>
       </c>
       <c r="F148" s="25" t="n">
-        <v>1225.715582</v>
+        <v>1234.617937</v>
       </c>
       <c r="G148" s="25" t="n">
-        <v>1458.243559</v>
+        <v>1468.599684</v>
       </c>
       <c r="H148" s="25" t="n">
-        <v>1719.9375</v>
+        <v>1731.945342</v>
       </c>
     </row>
     <row r="149">
@@ -5514,19 +5514,19 @@
         <v>-0.01</v>
       </c>
       <c r="D149" s="25" t="n">
-        <v>1053.411478</v>
+        <v>1060.919008</v>
       </c>
       <c r="E149" s="25" t="n">
-        <v>1268.007963</v>
+        <v>1276.821503</v>
       </c>
       <c r="F149" s="25" t="n">
-        <v>1511.217592</v>
+        <v>1521.528789</v>
       </c>
       <c r="G149" s="25" t="n">
-        <v>1786.484662</v>
+        <v>1798.509352</v>
       </c>
       <c r="H149" s="25" t="n">
-        <v>2097.599101</v>
+        <v>2111.579808</v>
       </c>
     </row>
     <row r="150">
@@ -5534,19 +5534,19 @@
         <v>0</v>
       </c>
       <c r="D150" s="25" t="n">
-        <v>1270.132238</v>
+        <v>1278.639614</v>
       </c>
       <c r="E150" s="25" t="n">
-        <v>1516.590087</v>
+        <v>1526.591321</v>
       </c>
       <c r="F150" s="25" t="n">
-        <v>1796.719602</v>
+        <v>1808.439641</v>
       </c>
       <c r="G150" s="25" t="n">
-        <v>2114.725766</v>
+        <v>2128.419021</v>
       </c>
       <c r="H150" s="25" t="n">
-        <v>2475.260702</v>
+        <v>2491.214274</v>
       </c>
     </row>
     <row r="151">
@@ -5554,19 +5554,19 @@
         <v>0.01</v>
       </c>
       <c r="D151" s="25" t="n">
-        <v>1486.852998</v>
+        <v>1496.36022</v>
       </c>
       <c r="E151" s="25" t="n">
-        <v>1765.172211</v>
+        <v>1776.36114</v>
       </c>
       <c r="F151" s="25" t="n">
-        <v>2082.221612</v>
+        <v>2095.350492</v>
       </c>
       <c r="G151" s="25" t="n">
-        <v>2442.966869</v>
+        <v>2458.328689</v>
       </c>
       <c r="H151" s="25" t="n">
-        <v>2852.922304</v>
+        <v>2870.84874</v>
       </c>
     </row>
     <row r="152">
@@ -5574,19 +5574,19 @@
         <v>0.02</v>
       </c>
       <c r="D152" s="25" t="n">
-        <v>1703.573758</v>
+        <v>1714.080826</v>
       </c>
       <c r="E152" s="25" t="n">
-        <v>2013.754335</v>
+        <v>2026.130958</v>
       </c>
       <c r="F152" s="25" t="n">
-        <v>2367.723623</v>
+        <v>2382.261344</v>
       </c>
       <c r="G152" s="25" t="n">
-        <v>2771.207973</v>
+        <v>2788.238358</v>
       </c>
       <c r="H152" s="25" t="n">
-        <v>3230.583905</v>
+        <v>3250.483206</v>
       </c>
     </row>
   </sheetData>

--- a/models/CHEMICALS.xlsx
+++ b/models/CHEMICALS.xlsx
@@ -489,7 +489,7 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>Generated 2026-10-29T23:12:35+07:00 by the coverage engine. The engine (scripts/cov_engine.py) is the source of truth; this workbook is a live rendering of it.</t>
+          <t>Generated 2026-10-30T04:49:02+07:00 by the coverage engine. The engine (scripts/cov_engine.py) is the source of truth; this workbook is a live rendering of it.</t>
         </is>
       </c>
     </row>
@@ -1017,13 +1017,13 @@
         <v/>
       </c>
       <c r="H2" s="9" t="n">
-        <v>15.344871</v>
+        <v>14.12436</v>
       </c>
       <c r="I2" s="9" t="n">
-        <v>8.665683</v>
+        <v>8.454827999999999</v>
       </c>
       <c r="J2" s="10" t="n">
-        <v>0.006517</v>
+        <v>0.00708</v>
       </c>
     </row>
   </sheetData>
@@ -1055,7 +1055,7 @@
     <row r="2">
       <c r="A2" s="5" t="inlineStr">
         <is>
-          <t>Units: USD m; per-share in USD unless marked IDR. Model asof 2026-10-29 · data 2026-10-27</t>
+          <t>Units: USD m; per-share in USD unless marked IDR. Model asof 2026-10-30 · data 2026-10-30</t>
         </is>
       </c>
     </row>
@@ -1301,34 +1301,34 @@
         </is>
       </c>
       <c r="H15" s="4" t="n">
-        <v>0.062</v>
+        <v>0.0635</v>
       </c>
       <c r="I15" s="4" t="n">
-        <v>0.062</v>
+        <v>0.0635</v>
       </c>
       <c r="J15" s="4" t="n">
-        <v>0.062</v>
+        <v>0.0635</v>
       </c>
       <c r="K15" s="4" t="n">
-        <v>0.062</v>
+        <v>0.0635</v>
       </c>
       <c r="L15" s="4" t="n">
-        <v>0.062</v>
+        <v>0.0635</v>
       </c>
       <c r="M15" s="4" t="n">
-        <v>0.062</v>
+        <v>0.0635</v>
       </c>
       <c r="N15" s="4" t="n">
-        <v>0.062</v>
+        <v>0.0635</v>
       </c>
       <c r="O15" s="4" t="n">
-        <v>0.062</v>
+        <v>0.0635</v>
       </c>
       <c r="P15" s="4" t="n">
-        <v>0.062</v>
+        <v>0.0635</v>
       </c>
       <c r="Q15" s="4" t="n">
-        <v>0.062</v>
+        <v>0.0635</v>
       </c>
     </row>
     <row r="16">
@@ -1427,34 +1427,34 @@
         </is>
       </c>
       <c r="H18" s="4" t="n">
-        <v>0.1</v>
+        <v>0.128</v>
       </c>
       <c r="I18" s="4" t="n">
-        <v>0.09</v>
+        <v>0.128</v>
       </c>
       <c r="J18" s="4" t="n">
-        <v>0.09</v>
+        <v>0.128</v>
       </c>
       <c r="K18" s="4" t="n">
-        <v>0.09</v>
+        <v>0.128</v>
       </c>
       <c r="L18" s="4" t="n">
-        <v>0.09</v>
+        <v>0.128</v>
       </c>
       <c r="M18" s="4" t="n">
-        <v>0.09</v>
+        <v>0.128</v>
       </c>
       <c r="N18" s="4" t="n">
-        <v>0.09</v>
+        <v>0.128</v>
       </c>
       <c r="O18" s="4" t="n">
-        <v>0.09</v>
+        <v>0.128</v>
       </c>
       <c r="P18" s="4" t="n">
-        <v>0.09</v>
+        <v>0.128</v>
       </c>
       <c r="Q18" s="4" t="n">
-        <v>0.09</v>
+        <v>0.128</v>
       </c>
     </row>
     <row r="19">
@@ -4615,7 +4615,7 @@
         </is>
       </c>
       <c r="C77" s="16" t="n">
-        <v>1500</v>
+        <v>1350</v>
       </c>
     </row>
     <row r="78">
@@ -4685,7 +4685,7 @@
         </is>
       </c>
       <c r="C84" s="13" t="n">
-        <v>935.5</v>
+        <v>650.3579999999999</v>
       </c>
     </row>
     <row r="85">
@@ -4768,7 +4768,7 @@
         </is>
       </c>
       <c r="C92" s="22" t="n">
-        <v>0.8260479760933566</v>
+        <v>0.917831084548174</v>
       </c>
     </row>
     <row r="93">
@@ -4889,31 +4889,31 @@
         <v>0</v>
       </c>
       <c r="I102" s="12" t="n">
-        <v>0.673511</v>
+        <v>0.670773</v>
       </c>
       <c r="J102" s="12" t="n">
-        <v>1.672827</v>
+        <v>1.670089</v>
       </c>
       <c r="K102" s="12" t="n">
-        <v>2.67488</v>
+        <v>2.672142</v>
       </c>
       <c r="L102" s="12" t="n">
-        <v>3.674196</v>
+        <v>3.671458</v>
       </c>
       <c r="M102" s="12" t="n">
-        <v>4.673511</v>
+        <v>4.670773</v>
       </c>
       <c r="N102" s="12" t="n">
-        <v>5.672827</v>
+        <v>5.670089</v>
       </c>
       <c r="O102" s="12" t="n">
-        <v>6.67488</v>
+        <v>6.672142</v>
       </c>
       <c r="P102" s="12" t="n">
-        <v>7.674196</v>
+        <v>7.671458</v>
       </c>
       <c r="Q102" s="12" t="n">
-        <v>8.673511</v>
+        <v>8.670773000000001</v>
       </c>
     </row>
     <row r="103">
@@ -5028,7 +5028,7 @@
         </is>
       </c>
       <c r="C106" s="21" t="n">
-        <v>9.171799999999999</v>
+        <v>9.169062</v>
       </c>
     </row>
     <row r="107">
@@ -5121,7 +5121,7 @@
         </is>
       </c>
       <c r="C116" s="16" t="n">
-        <v>9.775253070835372</v>
+        <v>9.557955490307522</v>
       </c>
     </row>
     <row r="117">
@@ -5152,7 +5152,7 @@
         </is>
       </c>
       <c r="C119" s="16" t="n">
-        <v>625.4777962626439</v>
+        <v>481.6905659871932</v>
       </c>
     </row>
     <row r="120">
@@ -5182,7 +5182,7 @@
         </is>
       </c>
       <c r="C122" s="16" t="n">
-        <v>3630.117672182625</v>
+        <v>3358.669456930156</v>
       </c>
     </row>
     <row r="123">
@@ -5224,7 +5224,7 @@
         </is>
       </c>
       <c r="C126" s="19" t="n">
-        <v>0.871427</v>
+        <v>0.876407</v>
       </c>
     </row>
     <row r="127">
@@ -5365,19 +5365,19 @@
         <v>-0.01</v>
       </c>
       <c r="D140" s="25" t="n">
-        <v>1706.816609</v>
+        <v>1528.50522</v>
       </c>
       <c r="E140" s="25" t="n">
-        <v>1575.111024</v>
+        <v>1400.305412</v>
       </c>
       <c r="F140" s="25" t="n">
-        <v>1457.898613</v>
+        <v>1286.251414</v>
       </c>
       <c r="G140" s="25" t="n">
-        <v>1352.916323</v>
+        <v>1184.129282</v>
       </c>
       <c r="H140" s="25" t="n">
-        <v>1258.348095</v>
+        <v>1092.163337</v>
       </c>
     </row>
     <row r="141">
@@ -5385,19 +5385,19 @@
         <v>-0.005</v>
       </c>
       <c r="D141" s="25" t="n">
-        <v>1786.965755</v>
+        <v>1606.709622</v>
       </c>
       <c r="E141" s="25" t="n">
-        <v>1643.394726</v>
+        <v>1466.909595</v>
       </c>
       <c r="F141" s="25" t="n">
-        <v>1516.500075</v>
+        <v>1343.394276</v>
       </c>
       <c r="G141" s="25" t="n">
-        <v>1403.537483</v>
+        <v>1233.477211</v>
       </c>
       <c r="H141" s="25" t="n">
-        <v>1302.332646</v>
+        <v>1135.031253</v>
       </c>
     </row>
     <row r="142">
@@ -5405,19 +5405,19 @@
         <v>0</v>
       </c>
       <c r="D142" s="25" t="n">
-        <v>1878.343454</v>
+        <v>1695.905099</v>
       </c>
       <c r="E142" s="25" t="n">
-        <v>1720.618452</v>
+        <v>1542.25992</v>
       </c>
       <c r="F142" s="25" t="n">
-        <v>1582.302524</v>
+        <v>1407.578543</v>
       </c>
       <c r="G142" s="25" t="n">
-        <v>1460.018946</v>
+        <v>1288.553105</v>
       </c>
       <c r="H142" s="25" t="n">
-        <v>1351.130577</v>
+        <v>1182.602041</v>
       </c>
     </row>
     <row r="143">
@@ -5425,19 +5425,19 @@
         <v>0.005</v>
       </c>
       <c r="D143" s="25" t="n">
-        <v>1983.487049</v>
+        <v>1798.583857</v>
       </c>
       <c r="E143" s="25" t="n">
-        <v>1808.660893</v>
+        <v>1628.200198</v>
       </c>
       <c r="F143" s="25" t="n">
-        <v>1656.72014</v>
+        <v>1480.191179</v>
       </c>
       <c r="G143" s="25" t="n">
-        <v>1523.440888</v>
+        <v>1350.415702</v>
       </c>
       <c r="H143" s="25" t="n">
-        <v>1405.577739</v>
+        <v>1235.694514</v>
       </c>
     </row>
     <row r="144">
@@ -5445,19 +5445,19 @@
         <v>0.01</v>
       </c>
       <c r="D144" s="25" t="n">
-        <v>2105.760652</v>
+        <v>1918.053181</v>
       </c>
       <c r="E144" s="25" t="n">
-        <v>1909.966778</v>
+        <v>1727.131685</v>
       </c>
       <c r="F144" s="25" t="n">
-        <v>1741.563346</v>
+        <v>1563.009007</v>
       </c>
       <c r="G144" s="25" t="n">
-        <v>1595.166331</v>
+        <v>1420.401799</v>
       </c>
       <c r="H144" s="25" t="n">
-        <v>1466.715405</v>
+        <v>1295.329285</v>
       </c>
     </row>
     <row r="146">
@@ -5494,19 +5494,19 @@
         <v>-0.02</v>
       </c>
       <c r="D148" s="25" t="n">
-        <v>843.198402</v>
+        <v>700.8235519999999</v>
       </c>
       <c r="E148" s="25" t="n">
-        <v>1027.051685</v>
+        <v>859.802785</v>
       </c>
       <c r="F148" s="25" t="n">
-        <v>1234.617937</v>
+        <v>1036.279215</v>
       </c>
       <c r="G148" s="25" t="n">
-        <v>1468.599684</v>
+        <v>1231.662478</v>
       </c>
       <c r="H148" s="25" t="n">
-        <v>1731.945342</v>
+        <v>1447.38709</v>
       </c>
     </row>
     <row r="149">
@@ -5514,19 +5514,19 @@
         <v>-0.01</v>
       </c>
       <c r="D149" s="25" t="n">
-        <v>1060.919008</v>
+        <v>919.956538</v>
       </c>
       <c r="E149" s="25" t="n">
-        <v>1276.821503</v>
+        <v>1111.221082</v>
       </c>
       <c r="F149" s="25" t="n">
-        <v>1521.528789</v>
+        <v>1325.114579</v>
       </c>
       <c r="G149" s="25" t="n">
-        <v>1798.509352</v>
+        <v>1563.818822</v>
       </c>
       <c r="H149" s="25" t="n">
-        <v>2111.579808</v>
+        <v>1829.643564</v>
       </c>
     </row>
     <row r="150">
@@ -5534,19 +5534,19 @@
         <v>0</v>
       </c>
       <c r="D150" s="25" t="n">
-        <v>1278.639614</v>
+        <v>1139.089524</v>
       </c>
       <c r="E150" s="25" t="n">
-        <v>1526.591321</v>
+        <v>1362.639379</v>
       </c>
       <c r="F150" s="25" t="n">
-        <v>1808.439641</v>
+        <v>1613.949942</v>
       </c>
       <c r="G150" s="25" t="n">
-        <v>2128.419021</v>
+        <v>1895.975165</v>
       </c>
       <c r="H150" s="25" t="n">
-        <v>2491.214274</v>
+        <v>2211.900037</v>
       </c>
     </row>
     <row r="151">
@@ -5554,19 +5554,19 @@
         <v>0.01</v>
       </c>
       <c r="D151" s="25" t="n">
-        <v>1496.36022</v>
+        <v>1358.222511</v>
       </c>
       <c r="E151" s="25" t="n">
-        <v>1776.36114</v>
+        <v>1614.057675</v>
       </c>
       <c r="F151" s="25" t="n">
-        <v>2095.350492</v>
+        <v>1902.785306</v>
       </c>
       <c r="G151" s="25" t="n">
-        <v>2458.328689</v>
+        <v>2228.131509</v>
       </c>
       <c r="H151" s="25" t="n">
-        <v>2870.84874</v>
+        <v>2594.15651</v>
       </c>
     </row>
     <row r="152">
@@ -5574,19 +5574,19 @@
         <v>0.02</v>
       </c>
       <c r="D152" s="25" t="n">
-        <v>1714.080826</v>
+        <v>1577.355497</v>
       </c>
       <c r="E152" s="25" t="n">
-        <v>2026.130958</v>
+        <v>1865.475972</v>
       </c>
       <c r="F152" s="25" t="n">
-        <v>2382.261344</v>
+        <v>2191.620669</v>
       </c>
       <c r="G152" s="25" t="n">
-        <v>2788.238358</v>
+        <v>2560.287853</v>
       </c>
       <c r="H152" s="25" t="n">
-        <v>3250.483206</v>
+        <v>2976.412984</v>
       </c>
     </row>
   </sheetData>

--- a/models/CHEMICALS.xlsx
+++ b/models/CHEMICALS.xlsx
@@ -489,7 +489,7 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>Generated 2026-10-30T04:49:02+07:00 by the coverage engine. The engine (scripts/cov_engine.py) is the source of truth; this workbook is a live rendering of it.</t>
+          <t>Generated 2026-10-30T15:34:59+07:00 by the coverage engine. The engine (scripts/cov_engine.py) is the source of truth; this workbook is a live rendering of it.</t>
         </is>
       </c>
     </row>
@@ -808,7 +808,7 @@
         </is>
       </c>
       <c r="C9" s="4" t="n">
-        <v>0.05009</v>
+        <v>0.04989</v>
       </c>
       <c r="D9" s="5" t="inlineStr">
         <is>
@@ -832,7 +832,7 @@
       </c>
       <c r="D10" s="5" t="inlineStr">
         <is>
-          <t>Damodaran country risk premiums (https://pages.stern.nyu.edu/~adamodar/New_Home_Page/datafile/ctryprem.html), page dated January 5, 2026, read 2026-10-29</t>
+          <t>Damodaran country risk premiums (https://pages.stern.nyu.edu/~adamodar/New_Home_Page/datafile/ctryprem.html), page dated January 5, 2026, read 2026-10-30</t>
         </is>
       </c>
     </row>
@@ -852,7 +852,7 @@
       </c>
       <c r="D11" s="5" t="inlineStr">
         <is>
-          <t>Damodaran country risk premiums (https://pages.stern.nyu.edu/~adamodar/New_Home_Page/datafile/ctryprem.html), page dated January 5, 2026, read 2026-10-29</t>
+          <t>Damodaran country risk premiums (https://pages.stern.nyu.edu/~adamodar/New_Home_Page/datafile/ctryprem.html), page dated January 5, 2026, read 2026-10-30</t>
         </is>
       </c>
     </row>
@@ -872,7 +872,7 @@
       </c>
       <c r="D12" s="5" t="inlineStr">
         <is>
-          <t>Damodaran country risk premiums (https://pages.stern.nyu.edu/~adamodar/New_Home_Page/datafile/ctryprem.html), page dated January 5, 2026, read 2026-10-29</t>
+          <t>Damodaran country risk premiums (https://pages.stern.nyu.edu/~adamodar/New_Home_Page/datafile/ctryprem.html), page dated January 5, 2026, read 2026-10-30</t>
         </is>
       </c>
     </row>
@@ -1017,13 +1017,13 @@
         <v/>
       </c>
       <c r="H2" s="9" t="n">
-        <v>14.12436</v>
+        <v>16.977483</v>
       </c>
       <c r="I2" s="9" t="n">
-        <v>8.454827999999999</v>
+        <v>9.499769000000001</v>
       </c>
       <c r="J2" s="10" t="n">
-        <v>0.00708</v>
+        <v>0.00589</v>
       </c>
     </row>
   </sheetData>
@@ -1187,10 +1187,10 @@
         </is>
       </c>
       <c r="H11" s="4" t="n">
-        <v>0.52</v>
+        <v>0.576</v>
       </c>
       <c r="I11" s="4" t="n">
-        <v>0.03</v>
+        <v>0.05</v>
       </c>
       <c r="J11" s="4" t="n">
         <v>0.03</v>
@@ -1229,34 +1229,34 @@
         </is>
       </c>
       <c r="H12" s="4" t="n">
-        <v>0.191</v>
+        <v>0.175</v>
       </c>
       <c r="I12" s="4" t="n">
-        <v>0.191</v>
+        <v>0.175</v>
       </c>
       <c r="J12" s="4" t="n">
-        <v>0.191</v>
+        <v>0.175</v>
       </c>
       <c r="K12" s="4" t="n">
-        <v>0.191</v>
+        <v>0.175</v>
       </c>
       <c r="L12" s="4" t="n">
-        <v>0.191</v>
+        <v>0.175</v>
       </c>
       <c r="M12" s="4" t="n">
-        <v>0.191</v>
+        <v>0.175</v>
       </c>
       <c r="N12" s="4" t="n">
-        <v>0.191</v>
+        <v>0.175</v>
       </c>
       <c r="O12" s="4" t="n">
-        <v>0.191</v>
+        <v>0.175</v>
       </c>
       <c r="P12" s="4" t="n">
-        <v>0.191</v>
+        <v>0.175</v>
       </c>
       <c r="Q12" s="4" t="n">
-        <v>0.191</v>
+        <v>0.175</v>
       </c>
     </row>
     <row r="13">
@@ -1385,7 +1385,7 @@
         </is>
       </c>
       <c r="H17" s="4" t="n">
-        <v>0.055</v>
+        <v>0.06900000000000001</v>
       </c>
       <c r="I17" s="4" t="n">
         <v>0.055</v>
@@ -1427,7 +1427,7 @@
         </is>
       </c>
       <c r="H18" s="4" t="n">
-        <v>0.128</v>
+        <v>0.099</v>
       </c>
       <c r="I18" s="4" t="n">
         <v>0.128</v>
@@ -1469,34 +1469,34 @@
         </is>
       </c>
       <c r="H19" s="4" t="n">
-        <v>0.145</v>
+        <v>0.035</v>
       </c>
       <c r="I19" s="4" t="n">
-        <v>0.16</v>
+        <v>0.07000000000000001</v>
       </c>
       <c r="J19" s="4" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="K19" s="4" t="n">
+        <v>0.13</v>
+      </c>
+      <c r="L19" s="4" t="n">
+        <v>0.15</v>
+      </c>
+      <c r="M19" s="4" t="n">
         <v>0.18</v>
       </c>
-      <c r="K19" s="4" t="n">
-        <v>0.2</v>
-      </c>
-      <c r="L19" s="4" t="n">
-        <v>0.2</v>
-      </c>
-      <c r="M19" s="4" t="n">
-        <v>0.2</v>
-      </c>
       <c r="N19" s="4" t="n">
-        <v>0.2</v>
+        <v>0.18</v>
       </c>
       <c r="O19" s="4" t="n">
-        <v>0.2</v>
+        <v>0.18</v>
       </c>
       <c r="P19" s="4" t="n">
-        <v>0.2</v>
+        <v>0.18</v>
       </c>
       <c r="Q19" s="4" t="n">
-        <v>0.2</v>
+        <v>0.18</v>
       </c>
     </row>
     <row r="20">
@@ -1511,7 +1511,7 @@
         </is>
       </c>
       <c r="C20" s="4" t="n">
-        <v>0.064</v>
+        <v>0.06900000000000001</v>
       </c>
     </row>
     <row r="21">
@@ -1526,7 +1526,7 @@
         </is>
       </c>
       <c r="C21" s="4" t="n">
-        <v>0.042</v>
+        <v>0.05</v>
       </c>
     </row>
     <row r="22">
@@ -1541,7 +1541,7 @@
         </is>
       </c>
       <c r="H22" s="13" t="n">
-        <v>496.707</v>
+        <v>679.649</v>
       </c>
       <c r="I22" s="13" t="n">
         <v>0</v>
@@ -1625,34 +1625,34 @@
         </is>
       </c>
       <c r="H24" s="4" t="n">
-        <v>0.24</v>
+        <v>0.28</v>
       </c>
       <c r="I24" s="4" t="n">
-        <v>0.24</v>
+        <v>0.28</v>
       </c>
       <c r="J24" s="4" t="n">
-        <v>0.24</v>
+        <v>0.28</v>
       </c>
       <c r="K24" s="4" t="n">
-        <v>0.24</v>
+        <v>0.28</v>
       </c>
       <c r="L24" s="4" t="n">
-        <v>0.24</v>
+        <v>0.28</v>
       </c>
       <c r="M24" s="4" t="n">
-        <v>0.24</v>
+        <v>0.28</v>
       </c>
       <c r="N24" s="4" t="n">
-        <v>0.24</v>
+        <v>0.28</v>
       </c>
       <c r="O24" s="4" t="n">
-        <v>0.24</v>
+        <v>0.28</v>
       </c>
       <c r="P24" s="4" t="n">
-        <v>0.24</v>
+        <v>0.28</v>
       </c>
       <c r="Q24" s="4" t="n">
-        <v>0.24</v>
+        <v>0.28</v>
       </c>
     </row>
     <row r="25">
@@ -4635,7 +4635,7 @@
         </is>
       </c>
       <c r="C79" s="3" t="n">
-        <v>18125</v>
+        <v>18130</v>
       </c>
     </row>
     <row r="80">
@@ -4645,7 +4645,7 @@
         </is>
       </c>
       <c r="C80" s="13" t="n">
-        <v>5910.937</v>
+        <v>6093.879</v>
       </c>
     </row>
     <row r="81">
@@ -4655,7 +4655,7 @@
         </is>
       </c>
       <c r="C81" s="13" t="n">
-        <v>2921.331</v>
+        <v>2962.669</v>
       </c>
     </row>
     <row r="82">
@@ -4665,7 +4665,7 @@
         </is>
       </c>
       <c r="C82" s="13" t="n">
-        <v>1003.746</v>
+        <v>1036.524</v>
       </c>
     </row>
     <row r="83">
@@ -4675,7 +4675,7 @@
         </is>
       </c>
       <c r="C83" s="13" t="n">
-        <v>174.831</v>
+        <v>210.956</v>
       </c>
     </row>
     <row r="84">
@@ -4685,7 +4685,7 @@
         </is>
       </c>
       <c r="C84" s="13" t="n">
-        <v>650.3579999999999</v>
+        <v>497.4370000000001</v>
       </c>
     </row>
     <row r="85">
@@ -4768,7 +4768,7 @@
         </is>
       </c>
       <c r="C92" s="22" t="n">
-        <v>0.917831084548174</v>
+        <v>0.9464987547727106</v>
       </c>
     </row>
     <row r="93">
@@ -5121,7 +5121,7 @@
         </is>
       </c>
       <c r="C116" s="16" t="n">
-        <v>9.557955490307522</v>
+        <v>7.951708910558592</v>
       </c>
     </row>
     <row r="117">
@@ -5152,7 +5152,7 @@
         </is>
       </c>
       <c r="C119" s="16" t="n">
-        <v>481.6905659871932</v>
+        <v>0</v>
       </c>
     </row>
     <row r="120">
@@ -5182,7 +5182,7 @@
         </is>
       </c>
       <c r="C122" s="16" t="n">
-        <v>3358.669456930156</v>
+        <v>2862.838954484247</v>
       </c>
     </row>
     <row r="123">
@@ -5224,7 +5224,7 @@
         </is>
       </c>
       <c r="C126" s="19" t="n">
-        <v>0.876407</v>
+        <v>1.150816</v>
       </c>
     </row>
     <row r="127">
@@ -5244,7 +5244,7 @@
         </is>
       </c>
       <c r="C128" s="4" t="n">
-        <v>-0.15</v>
+        <v>0.7</v>
       </c>
     </row>
     <row r="129">
@@ -5284,7 +5284,7 @@
         </is>
       </c>
       <c r="C132" s="4" t="n">
-        <v>0.7</v>
+        <v>-0.15</v>
       </c>
     </row>
     <row r="133">
@@ -5365,19 +5365,19 @@
         <v>-0.01</v>
       </c>
       <c r="D140" s="25" t="n">
-        <v>1528.50522</v>
+        <v>1207.544467</v>
       </c>
       <c r="E140" s="25" t="n">
-        <v>1400.305412</v>
+        <v>1092.948524</v>
       </c>
       <c r="F140" s="25" t="n">
-        <v>1286.251414</v>
+        <v>990.999204</v>
       </c>
       <c r="G140" s="25" t="n">
-        <v>1184.129282</v>
+        <v>899.7135029999999</v>
       </c>
       <c r="H140" s="25" t="n">
-        <v>1092.163337</v>
+        <v>817.5018659999999</v>
       </c>
     </row>
     <row r="141">
@@ -5385,19 +5385,19 @@
         <v>-0.005</v>
       </c>
       <c r="D141" s="25" t="n">
-        <v>1606.709622</v>
+        <v>1277.366397</v>
       </c>
       <c r="E141" s="25" t="n">
-        <v>1466.909595</v>
+        <v>1152.390847</v>
       </c>
       <c r="F141" s="25" t="n">
-        <v>1343.394276</v>
+        <v>1041.980203</v>
       </c>
       <c r="G141" s="25" t="n">
-        <v>1233.477211</v>
+        <v>943.7266959999999</v>
       </c>
       <c r="H141" s="25" t="n">
-        <v>1135.031253</v>
+        <v>855.725066</v>
       </c>
     </row>
     <row r="142">
@@ -5405,19 +5405,19 @@
         <v>0</v>
       </c>
       <c r="D142" s="25" t="n">
-        <v>1695.905099</v>
+        <v>1357.035231</v>
       </c>
       <c r="E142" s="25" t="n">
-        <v>1542.25992</v>
+        <v>1219.66406</v>
       </c>
       <c r="F142" s="25" t="n">
-        <v>1407.578543</v>
+        <v>1099.262349</v>
       </c>
       <c r="G142" s="25" t="n">
-        <v>1288.553105</v>
+        <v>992.863213</v>
       </c>
       <c r="H142" s="25" t="n">
-        <v>1182.602041</v>
+        <v>898.152891</v>
       </c>
     </row>
     <row r="143">
@@ -5425,19 +5425,19 @@
         <v>0.005</v>
       </c>
       <c r="D143" s="25" t="n">
-        <v>1798.583857</v>
+        <v>1448.792043</v>
       </c>
       <c r="E143" s="25" t="n">
-        <v>1628.200198</v>
+        <v>1296.424735</v>
       </c>
       <c r="F143" s="25" t="n">
-        <v>1480.191179</v>
+        <v>1164.090805</v>
       </c>
       <c r="G143" s="25" t="n">
-        <v>1350.415702</v>
+        <v>1048.072903</v>
       </c>
       <c r="H143" s="25" t="n">
-        <v>1235.694514</v>
+        <v>945.519497</v>
       </c>
     </row>
     <row r="144">
@@ -5445,19 +5445,19 @@
         <v>0.01</v>
       </c>
       <c r="D144" s="25" t="n">
-        <v>1918.053181</v>
+        <v>1555.613802</v>
       </c>
       <c r="E144" s="25" t="n">
-        <v>1727.131685</v>
+        <v>1384.83214</v>
       </c>
       <c r="F144" s="25" t="n">
-        <v>1563.009007</v>
+        <v>1238.061942</v>
       </c>
       <c r="G144" s="25" t="n">
-        <v>1420.401799</v>
+        <v>1110.555879</v>
       </c>
       <c r="H144" s="25" t="n">
-        <v>1295.329285</v>
+        <v>998.740518</v>
       </c>
     </row>
     <row r="146">
@@ -5494,19 +5494,19 @@
         <v>-0.02</v>
       </c>
       <c r="D148" s="25" t="n">
-        <v>700.8235519999999</v>
+        <v>369.40677</v>
       </c>
       <c r="E148" s="25" t="n">
-        <v>859.802785</v>
+        <v>489.630476</v>
       </c>
       <c r="F148" s="25" t="n">
-        <v>1036.279215</v>
+        <v>620.548523</v>
       </c>
       <c r="G148" s="25" t="n">
-        <v>1231.662478</v>
+        <v>762.46626</v>
       </c>
       <c r="H148" s="25" t="n">
-        <v>1447.38709</v>
+        <v>915.558602</v>
       </c>
     </row>
     <row r="149">
@@ -5514,19 +5514,19 @@
         <v>-0.01</v>
       </c>
       <c r="D149" s="25" t="n">
-        <v>919.956538</v>
+        <v>613.702885</v>
       </c>
       <c r="E149" s="25" t="n">
-        <v>1111.221082</v>
+        <v>769.168131</v>
       </c>
       <c r="F149" s="25" t="n">
-        <v>1325.114579</v>
+        <v>940.875727</v>
       </c>
       <c r="G149" s="25" t="n">
-        <v>1563.818822</v>
+        <v>1129.960716</v>
       </c>
       <c r="H149" s="25" t="n">
-        <v>1829.643564</v>
+        <v>1337.537866</v>
       </c>
     </row>
     <row r="150">
@@ -5534,19 +5534,19 @@
         <v>0</v>
       </c>
       <c r="D150" s="25" t="n">
-        <v>1139.089524</v>
+        <v>857.999</v>
       </c>
       <c r="E150" s="25" t="n">
-        <v>1362.639379</v>
+        <v>1048.705785</v>
       </c>
       <c r="F150" s="25" t="n">
-        <v>1613.949942</v>
+        <v>1261.202932</v>
       </c>
       <c r="G150" s="25" t="n">
-        <v>1895.975165</v>
+        <v>1497.455173</v>
       </c>
       <c r="H150" s="25" t="n">
-        <v>2211.900037</v>
+        <v>1759.51713</v>
       </c>
     </row>
     <row r="151">
@@ -5554,19 +5554,19 @@
         <v>0.01</v>
       </c>
       <c r="D151" s="25" t="n">
-        <v>1358.222511</v>
+        <v>1102.295115</v>
       </c>
       <c r="E151" s="25" t="n">
-        <v>1614.057675</v>
+        <v>1328.24344</v>
       </c>
       <c r="F151" s="25" t="n">
-        <v>1902.785306</v>
+        <v>1581.530136</v>
       </c>
       <c r="G151" s="25" t="n">
-        <v>2228.131509</v>
+        <v>1864.949629</v>
       </c>
       <c r="H151" s="25" t="n">
-        <v>2594.15651</v>
+        <v>2181.496395</v>
       </c>
     </row>
     <row r="152">
@@ -5574,19 +5574,19 @@
         <v>0.02</v>
       </c>
       <c r="D152" s="25" t="n">
-        <v>1577.355497</v>
+        <v>1346.591229</v>
       </c>
       <c r="E152" s="25" t="n">
-        <v>1865.475972</v>
+        <v>1607.781094</v>
       </c>
       <c r="F152" s="25" t="n">
-        <v>2191.620669</v>
+        <v>1901.857341</v>
       </c>
       <c r="G152" s="25" t="n">
-        <v>2560.287853</v>
+        <v>2232.444085</v>
       </c>
       <c r="H152" s="25" t="n">
-        <v>2976.412984</v>
+        <v>2603.475659</v>
       </c>
     </row>
   </sheetData>

--- a/models/CHEMICALS.xlsx
+++ b/models/CHEMICALS.xlsx
@@ -489,7 +489,7 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>Generated 2026-10-30T15:34:59+07:00 by the coverage engine. The engine (scripts/cov_engine.py) is the source of truth; this workbook is a live rendering of it.</t>
+          <t>Generated 2026-10-30T18:34:03+07:00 by the coverage engine. The engine (scripts/cov_engine.py) is the source of truth; this workbook is a live rendering of it.</t>
         </is>
       </c>
     </row>
@@ -4685,7 +4685,7 @@
         </is>
       </c>
       <c r="C84" s="13" t="n">
-        <v>497.4370000000001</v>
+        <v>497.051</v>
       </c>
     </row>
     <row r="85">
@@ -5182,7 +5182,7 @@
         </is>
       </c>
       <c r="C122" s="16" t="n">
-        <v>2862.838954484247</v>
+        <v>2862.745508534519</v>
       </c>
     </row>
     <row r="123">
@@ -5224,7 +5224,7 @@
         </is>
       </c>
       <c r="C126" s="19" t="n">
-        <v>1.150816</v>
+        <v>1.150875</v>
       </c>
     </row>
     <row r="127">
@@ -5365,19 +5365,19 @@
         <v>-0.01</v>
       </c>
       <c r="D140" s="25" t="n">
-        <v>1207.544467</v>
+        <v>1207.46353</v>
       </c>
       <c r="E140" s="25" t="n">
-        <v>1092.948524</v>
+        <v>1092.867587</v>
       </c>
       <c r="F140" s="25" t="n">
-        <v>990.999204</v>
+        <v>990.918267</v>
       </c>
       <c r="G140" s="25" t="n">
-        <v>899.7135029999999</v>
+        <v>899.632566</v>
       </c>
       <c r="H140" s="25" t="n">
-        <v>817.5018659999999</v>
+        <v>817.420929</v>
       </c>
     </row>
     <row r="141">
@@ -5385,19 +5385,19 @@
         <v>-0.005</v>
       </c>
       <c r="D141" s="25" t="n">
-        <v>1277.366397</v>
+        <v>1277.285459</v>
       </c>
       <c r="E141" s="25" t="n">
-        <v>1152.390847</v>
+        <v>1152.30991</v>
       </c>
       <c r="F141" s="25" t="n">
-        <v>1041.980203</v>
+        <v>1041.899266</v>
       </c>
       <c r="G141" s="25" t="n">
-        <v>943.7266959999999</v>
+        <v>943.645759</v>
       </c>
       <c r="H141" s="25" t="n">
-        <v>855.725066</v>
+        <v>855.644129</v>
       </c>
     </row>
     <row r="142">
@@ -5405,19 +5405,19 @@
         <v>0</v>
       </c>
       <c r="D142" s="25" t="n">
-        <v>1357.035231</v>
+        <v>1356.954293</v>
       </c>
       <c r="E142" s="25" t="n">
-        <v>1219.66406</v>
+        <v>1219.583123</v>
       </c>
       <c r="F142" s="25" t="n">
-        <v>1099.262349</v>
+        <v>1099.181412</v>
       </c>
       <c r="G142" s="25" t="n">
-        <v>992.863213</v>
+        <v>992.782276</v>
       </c>
       <c r="H142" s="25" t="n">
-        <v>898.152891</v>
+        <v>898.071954</v>
       </c>
     </row>
     <row r="143">
@@ -5425,19 +5425,19 @@
         <v>0.005</v>
       </c>
       <c r="D143" s="25" t="n">
-        <v>1448.792043</v>
+        <v>1448.711106</v>
       </c>
       <c r="E143" s="25" t="n">
-        <v>1296.424735</v>
+        <v>1296.343798</v>
       </c>
       <c r="F143" s="25" t="n">
-        <v>1164.090805</v>
+        <v>1164.009868</v>
       </c>
       <c r="G143" s="25" t="n">
-        <v>1048.072903</v>
+        <v>1047.991966</v>
       </c>
       <c r="H143" s="25" t="n">
-        <v>945.519497</v>
+        <v>945.4385600000001</v>
       </c>
     </row>
     <row r="144">
@@ -5445,19 +5445,19 @@
         <v>0.01</v>
       </c>
       <c r="D144" s="25" t="n">
-        <v>1555.613802</v>
+        <v>1555.532865</v>
       </c>
       <c r="E144" s="25" t="n">
-        <v>1384.83214</v>
+        <v>1384.751203</v>
       </c>
       <c r="F144" s="25" t="n">
-        <v>1238.061942</v>
+        <v>1237.981005</v>
       </c>
       <c r="G144" s="25" t="n">
-        <v>1110.555879</v>
+        <v>1110.474942</v>
       </c>
       <c r="H144" s="25" t="n">
-        <v>998.740518</v>
+        <v>998.659581</v>
       </c>
     </row>
     <row r="146">
@@ -5494,19 +5494,19 @@
         <v>-0.02</v>
       </c>
       <c r="D148" s="25" t="n">
-        <v>369.40677</v>
+        <v>369.313324</v>
       </c>
       <c r="E148" s="25" t="n">
-        <v>489.630476</v>
+        <v>489.53703</v>
       </c>
       <c r="F148" s="25" t="n">
-        <v>620.548523</v>
+        <v>620.455077</v>
       </c>
       <c r="G148" s="25" t="n">
-        <v>762.46626</v>
+        <v>762.3728139999999</v>
       </c>
       <c r="H148" s="25" t="n">
-        <v>915.558602</v>
+        <v>915.465156</v>
       </c>
     </row>
     <row r="149">
@@ -5514,19 +5514,19 @@
         <v>-0.01</v>
       </c>
       <c r="D149" s="25" t="n">
-        <v>613.702885</v>
+        <v>613.609439</v>
       </c>
       <c r="E149" s="25" t="n">
-        <v>769.168131</v>
+        <v>769.074685</v>
       </c>
       <c r="F149" s="25" t="n">
-        <v>940.875727</v>
+        <v>940.782281</v>
       </c>
       <c r="G149" s="25" t="n">
-        <v>1129.960716</v>
+        <v>1129.86727</v>
       </c>
       <c r="H149" s="25" t="n">
-        <v>1337.537866</v>
+        <v>1337.44442</v>
       </c>
     </row>
     <row r="150">
@@ -5534,19 +5534,19 @@
         <v>0</v>
       </c>
       <c r="D150" s="25" t="n">
-        <v>857.999</v>
+        <v>857.9055540000001</v>
       </c>
       <c r="E150" s="25" t="n">
-        <v>1048.705785</v>
+        <v>1048.612339</v>
       </c>
       <c r="F150" s="25" t="n">
-        <v>1261.202932</v>
+        <v>1261.109486</v>
       </c>
       <c r="G150" s="25" t="n">
-        <v>1497.455173</v>
+        <v>1497.361727</v>
       </c>
       <c r="H150" s="25" t="n">
-        <v>1759.51713</v>
+        <v>1759.423684</v>
       </c>
     </row>
     <row r="151">
@@ -5554,19 +5554,19 @@
         <v>0.01</v>
       </c>
       <c r="D151" s="25" t="n">
-        <v>1102.295115</v>
+        <v>1102.201669</v>
       </c>
       <c r="E151" s="25" t="n">
-        <v>1328.24344</v>
+        <v>1328.149994</v>
       </c>
       <c r="F151" s="25" t="n">
-        <v>1581.530136</v>
+        <v>1581.43669</v>
       </c>
       <c r="G151" s="25" t="n">
-        <v>1864.949629</v>
+        <v>1864.856183</v>
       </c>
       <c r="H151" s="25" t="n">
-        <v>2181.496395</v>
+        <v>2181.402949</v>
       </c>
     </row>
     <row r="152">
@@ -5574,19 +5574,19 @@
         <v>0.02</v>
       </c>
       <c r="D152" s="25" t="n">
-        <v>1346.591229</v>
+        <v>1346.497783</v>
       </c>
       <c r="E152" s="25" t="n">
-        <v>1607.781094</v>
+        <v>1607.687648</v>
       </c>
       <c r="F152" s="25" t="n">
-        <v>1901.857341</v>
+        <v>1901.763895</v>
       </c>
       <c r="G152" s="25" t="n">
-        <v>2232.444085</v>
+        <v>2232.350639</v>
       </c>
       <c r="H152" s="25" t="n">
-        <v>2603.475659</v>
+        <v>2603.382213</v>
       </c>
     </row>
   </sheetData>

--- a/models/CHEMICALS.xlsx
+++ b/models/CHEMICALS.xlsx
@@ -489,7 +489,7 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>Generated 2026-10-30T18:34:03+07:00 by the coverage engine. The engine (scripts/cov_engine.py) is the source of truth; this workbook is a live rendering of it.</t>
+          <t>Generated 2026-10-30T19:34:50+07:00 by the coverage engine. The engine (scripts/cov_engine.py) is the source of truth; this workbook is a live rendering of it.</t>
         </is>
       </c>
     </row>
@@ -1017,13 +1017,13 @@
         <v/>
       </c>
       <c r="H2" s="9" t="n">
-        <v>16.977483</v>
+        <v>16.969995</v>
       </c>
       <c r="I2" s="9" t="n">
-        <v>9.499769000000001</v>
+        <v>9.497237</v>
       </c>
       <c r="J2" s="10" t="n">
-        <v>0.00589</v>
+        <v>0.005893</v>
       </c>
     </row>
   </sheetData>
@@ -4635,7 +4635,7 @@
         </is>
       </c>
       <c r="C79" s="3" t="n">
-        <v>18130</v>
+        <v>18138</v>
       </c>
     </row>
     <row r="80">
@@ -4768,7 +4768,7 @@
         </is>
       </c>
       <c r="C92" s="22" t="n">
-        <v>0.9464987547727106</v>
+        <v>0.9469164045266092</v>
       </c>
     </row>
     <row r="93">
@@ -5121,7 +5121,7 @@
         </is>
       </c>
       <c r="C116" s="16" t="n">
-        <v>7.951708910558592</v>
+        <v>7.955217662422048</v>
       </c>
     </row>
     <row r="117">
@@ -5182,7 +5182,7 @@
         </is>
       </c>
       <c r="C122" s="16" t="n">
-        <v>2862.745508534519</v>
+        <v>2864.100025985348</v>
       </c>
     </row>
     <row r="123">
@@ -5224,7 +5224,7 @@
         </is>
       </c>
       <c r="C126" s="19" t="n">
-        <v>1.150875</v>
+        <v>1.150348</v>
       </c>
     </row>
     <row r="127">
@@ -5365,19 +5365,19 @@
         <v>-0.01</v>
       </c>
       <c r="D140" s="25" t="n">
-        <v>1207.46353</v>
+        <v>1208.019471</v>
       </c>
       <c r="E140" s="25" t="n">
-        <v>1092.867587</v>
+        <v>1093.370338</v>
       </c>
       <c r="F140" s="25" t="n">
-        <v>990.918267</v>
+        <v>991.373831</v>
       </c>
       <c r="G140" s="25" t="n">
-        <v>899.632566</v>
+        <v>900.045984</v>
       </c>
       <c r="H140" s="25" t="n">
-        <v>817.420929</v>
+        <v>817.796476</v>
       </c>
     </row>
     <row r="141">
@@ -5385,19 +5385,19 @@
         <v>-0.005</v>
       </c>
       <c r="D141" s="25" t="n">
-        <v>1277.285459</v>
+        <v>1277.8744</v>
       </c>
       <c r="E141" s="25" t="n">
-        <v>1152.30991</v>
+        <v>1152.840666</v>
       </c>
       <c r="F141" s="25" t="n">
-        <v>1041.899266</v>
+        <v>1042.378781</v>
       </c>
       <c r="G141" s="25" t="n">
-        <v>943.645759</v>
+        <v>944.079802</v>
       </c>
       <c r="H141" s="25" t="n">
-        <v>855.644129</v>
+        <v>856.037547</v>
       </c>
     </row>
     <row r="142">
@@ -5405,19 +5405,19 @@
         <v>0</v>
       </c>
       <c r="D142" s="25" t="n">
-        <v>1356.954293</v>
+        <v>1357.581019</v>
       </c>
       <c r="E142" s="25" t="n">
-        <v>1219.583123</v>
+        <v>1220.145672</v>
       </c>
       <c r="F142" s="25" t="n">
-        <v>1099.181412</v>
+        <v>1099.687913</v>
       </c>
       <c r="G142" s="25" t="n">
-        <v>992.782276</v>
+        <v>993.239402</v>
       </c>
       <c r="H142" s="25" t="n">
-        <v>898.071954</v>
+        <v>898.4852529999999</v>
       </c>
     </row>
     <row r="143">
@@ -5425,19 +5425,19 @@
         <v>0.005</v>
       </c>
       <c r="D143" s="25" t="n">
-        <v>1448.711106</v>
+        <v>1449.381524</v>
       </c>
       <c r="E143" s="25" t="n">
-        <v>1296.343798</v>
+        <v>1296.94275</v>
       </c>
       <c r="F143" s="25" t="n">
-        <v>1164.009868</v>
+        <v>1164.547003</v>
       </c>
       <c r="G143" s="25" t="n">
-        <v>1047.991966</v>
+        <v>1048.475099</v>
       </c>
       <c r="H143" s="25" t="n">
-        <v>945.4385600000001</v>
+        <v>945.874109</v>
       </c>
     </row>
     <row r="144">
@@ -5445,19 +5445,19 @@
         <v>0.01</v>
       </c>
       <c r="D144" s="25" t="n">
-        <v>1555.532865</v>
+        <v>1556.254384</v>
       </c>
       <c r="E144" s="25" t="n">
-        <v>1384.751203</v>
+        <v>1385.39225</v>
       </c>
       <c r="F144" s="25" t="n">
-        <v>1237.981005</v>
+        <v>1238.553218</v>
       </c>
       <c r="G144" s="25" t="n">
-        <v>1110.474942</v>
+        <v>1110.9876</v>
       </c>
       <c r="H144" s="25" t="n">
-        <v>998.659581</v>
+        <v>999.120199</v>
       </c>
     </row>
     <row r="146">
@@ -5494,19 +5494,19 @@
         <v>-0.02</v>
       </c>
       <c r="D148" s="25" t="n">
-        <v>369.313324</v>
+        <v>369.496489</v>
       </c>
       <c r="E148" s="25" t="n">
-        <v>489.53703</v>
+        <v>489.777155</v>
       </c>
       <c r="F148" s="25" t="n">
-        <v>620.455077</v>
+        <v>620.757248</v>
       </c>
       <c r="G148" s="25" t="n">
-        <v>762.3728139999999</v>
+        <v>762.742266</v>
       </c>
       <c r="H148" s="25" t="n">
-        <v>915.465156</v>
+        <v>915.907207</v>
       </c>
     </row>
     <row r="149">
@@ -5514,19 +5514,19 @@
         <v>-0.01</v>
       </c>
       <c r="D149" s="25" t="n">
-        <v>613.609439</v>
+        <v>613.907031</v>
       </c>
       <c r="E149" s="25" t="n">
-        <v>769.074685</v>
+        <v>769.445875</v>
       </c>
       <c r="F149" s="25" t="n">
-        <v>940.782281</v>
+        <v>941.234788</v>
       </c>
       <c r="G149" s="25" t="n">
-        <v>1129.86727</v>
+        <v>1130.409352</v>
       </c>
       <c r="H149" s="25" t="n">
-        <v>1337.44442</v>
+        <v>1338.084867</v>
       </c>
     </row>
     <row r="150">
@@ -5534,19 +5534,19 @@
         <v>0</v>
       </c>
       <c r="D150" s="25" t="n">
-        <v>857.9055540000001</v>
+        <v>858.317573</v>
       </c>
       <c r="E150" s="25" t="n">
-        <v>1048.612339</v>
+        <v>1049.114595</v>
       </c>
       <c r="F150" s="25" t="n">
-        <v>1261.109486</v>
+        <v>1261.712327</v>
       </c>
       <c r="G150" s="25" t="n">
-        <v>1497.361727</v>
+        <v>1498.076438</v>
       </c>
       <c r="H150" s="25" t="n">
-        <v>1759.423684</v>
+        <v>1760.262527</v>
       </c>
     </row>
     <row r="151">
@@ -5554,19 +5554,19 @@
         <v>0.01</v>
       </c>
       <c r="D151" s="25" t="n">
-        <v>1102.201669</v>
+        <v>1102.728115</v>
       </c>
       <c r="E151" s="25" t="n">
-        <v>1328.149994</v>
+        <v>1328.783315</v>
       </c>
       <c r="F151" s="25" t="n">
-        <v>1581.43669</v>
+        <v>1582.189867</v>
       </c>
       <c r="G151" s="25" t="n">
-        <v>1864.856183</v>
+        <v>1865.743524</v>
       </c>
       <c r="H151" s="25" t="n">
-        <v>2181.402949</v>
+        <v>2182.440187</v>
       </c>
     </row>
     <row r="152">
@@ -5574,19 +5574,19 @@
         <v>0.02</v>
       </c>
       <c r="D152" s="25" t="n">
-        <v>1346.497783</v>
+        <v>1347.138657</v>
       </c>
       <c r="E152" s="25" t="n">
-        <v>1607.687648</v>
+        <v>1608.452036</v>
       </c>
       <c r="F152" s="25" t="n">
-        <v>1901.763895</v>
+        <v>1902.667407</v>
       </c>
       <c r="G152" s="25" t="n">
-        <v>2232.350639</v>
+        <v>2233.410609</v>
       </c>
       <c r="H152" s="25" t="n">
-        <v>2603.382213</v>
+        <v>2604.617847</v>
       </c>
     </row>
   </sheetData>

--- a/models/CHEMICALS.xlsx
+++ b/models/CHEMICALS.xlsx
@@ -489,7 +489,7 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>Generated 2026-10-30T19:34:50+07:00 by the coverage engine. The engine (scripts/cov_engine.py) is the source of truth; this workbook is a live rendering of it.</t>
+          <t>Generated 2026-10-31T09:23:14+07:00 by the coverage engine. The engine (scripts/cov_engine.py) is the source of truth; this workbook is a live rendering of it.</t>
         </is>
       </c>
     </row>
@@ -808,7 +808,7 @@
         </is>
       </c>
       <c r="C9" s="4" t="n">
-        <v>0.04989</v>
+        <v>0.04929</v>
       </c>
       <c r="D9" s="5" t="inlineStr">
         <is>
@@ -832,7 +832,7 @@
       </c>
       <c r="D10" s="5" t="inlineStr">
         <is>
-          <t>Damodaran country risk premiums (https://pages.stern.nyu.edu/~adamodar/New_Home_Page/datafile/ctryprem.html), page dated January 5, 2026, read 2026-10-30</t>
+          <t>Damodaran country risk premiums (https://pages.stern.nyu.edu/~adamodar/New_Home_Page/datafile/ctryprem.html), page dated January 5, 2026, read 2026-10-31</t>
         </is>
       </c>
     </row>
@@ -852,7 +852,7 @@
       </c>
       <c r="D11" s="5" t="inlineStr">
         <is>
-          <t>Damodaran country risk premiums (https://pages.stern.nyu.edu/~adamodar/New_Home_Page/datafile/ctryprem.html), page dated January 5, 2026, read 2026-10-30</t>
+          <t>Damodaran country risk premiums (https://pages.stern.nyu.edu/~adamodar/New_Home_Page/datafile/ctryprem.html), page dated January 5, 2026, read 2026-10-31</t>
         </is>
       </c>
     </row>
@@ -872,7 +872,7 @@
       </c>
       <c r="D12" s="5" t="inlineStr">
         <is>
-          <t>Damodaran country risk premiums (https://pages.stern.nyu.edu/~adamodar/New_Home_Page/datafile/ctryprem.html), page dated January 5, 2026, read 2026-10-30</t>
+          <t>Damodaran country risk premiums (https://pages.stern.nyu.edu/~adamodar/New_Home_Page/datafile/ctryprem.html), page dated January 5, 2026, read 2026-10-31</t>
         </is>
       </c>
     </row>
@@ -1017,13 +1017,13 @@
         <v/>
       </c>
       <c r="H2" s="9" t="n">
-        <v>16.969995</v>
+        <v>129.583861</v>
       </c>
       <c r="I2" s="9" t="n">
-        <v>9.497237</v>
+        <v>17.1734</v>
       </c>
       <c r="J2" s="10" t="n">
-        <v>0.005893</v>
+        <v>0.000772</v>
       </c>
     </row>
   </sheetData>
@@ -1055,7 +1055,7 @@
     <row r="2">
       <c r="A2" s="5" t="inlineStr">
         <is>
-          <t>Units: USD m; per-share in USD unless marked IDR. Model asof 2026-10-30 · data 2026-10-30</t>
+          <t>Units: USD m; per-share in USD unless marked IDR. Model asof 2026-10-31 · data 2026-10-30</t>
         </is>
       </c>
     </row>
@@ -1229,34 +1229,34 @@
         </is>
       </c>
       <c r="H12" s="4" t="n">
-        <v>0.175</v>
+        <v>0.134</v>
       </c>
       <c r="I12" s="4" t="n">
-        <v>0.175</v>
+        <v>0.134</v>
       </c>
       <c r="J12" s="4" t="n">
-        <v>0.175</v>
+        <v>0.134</v>
       </c>
       <c r="K12" s="4" t="n">
-        <v>0.175</v>
+        <v>0.134</v>
       </c>
       <c r="L12" s="4" t="n">
-        <v>0.175</v>
+        <v>0.134</v>
       </c>
       <c r="M12" s="4" t="n">
-        <v>0.175</v>
+        <v>0.134</v>
       </c>
       <c r="N12" s="4" t="n">
-        <v>0.175</v>
+        <v>0.134</v>
       </c>
       <c r="O12" s="4" t="n">
-        <v>0.175</v>
+        <v>0.134</v>
       </c>
       <c r="P12" s="4" t="n">
-        <v>0.175</v>
+        <v>0.134</v>
       </c>
       <c r="Q12" s="4" t="n">
-        <v>0.175</v>
+        <v>0.134</v>
       </c>
     </row>
     <row r="13">
@@ -4685,7 +4685,7 @@
         </is>
       </c>
       <c r="C84" s="13" t="n">
-        <v>497.051</v>
+        <v>611.3810000000001</v>
       </c>
     </row>
     <row r="85">
@@ -4889,31 +4889,31 @@
         <v>0</v>
       </c>
       <c r="I102" s="12" t="n">
-        <v>0.670773</v>
+        <v>0.668036</v>
       </c>
       <c r="J102" s="12" t="n">
-        <v>1.670089</v>
+        <v>1.667351</v>
       </c>
       <c r="K102" s="12" t="n">
-        <v>2.672142</v>
+        <v>2.669405</v>
       </c>
       <c r="L102" s="12" t="n">
-        <v>3.671458</v>
+        <v>3.66872</v>
       </c>
       <c r="M102" s="12" t="n">
-        <v>4.670773</v>
+        <v>4.668036</v>
       </c>
       <c r="N102" s="12" t="n">
-        <v>5.670089</v>
+        <v>5.667351</v>
       </c>
       <c r="O102" s="12" t="n">
-        <v>6.672142</v>
+        <v>6.669405</v>
       </c>
       <c r="P102" s="12" t="n">
-        <v>7.671458</v>
+        <v>7.66872</v>
       </c>
       <c r="Q102" s="12" t="n">
-        <v>8.670773000000001</v>
+        <v>8.668036000000001</v>
       </c>
     </row>
     <row r="103">
@@ -5028,7 +5028,7 @@
         </is>
       </c>
       <c r="C106" s="21" t="n">
-        <v>9.169062</v>
+        <v>9.166325000000001</v>
       </c>
     </row>
     <row r="107">
@@ -5121,7 +5121,7 @@
         </is>
       </c>
       <c r="C116" s="16" t="n">
-        <v>7.955217662422048</v>
+        <v>1.04179640290296</v>
       </c>
     </row>
     <row r="117">
@@ -5142,7 +5142,7 @@
         </is>
       </c>
       <c r="C118" s="4" t="n">
-        <v>0.25</v>
+        <v>0.35</v>
       </c>
     </row>
     <row r="119">
@@ -5162,7 +5162,7 @@
         </is>
       </c>
       <c r="C120" s="4" t="n">
-        <v>0.5</v>
+        <v>0.45</v>
       </c>
     </row>
     <row r="121">
@@ -5172,7 +5172,7 @@
         </is>
       </c>
       <c r="C121" s="4" t="n">
-        <v>0.25</v>
+        <v>0.2</v>
       </c>
     </row>
     <row r="122">
@@ -5182,7 +5182,7 @@
         </is>
       </c>
       <c r="C122" s="16" t="n">
-        <v>2864.100025985348</v>
+        <v>1593.537265121418</v>
       </c>
     </row>
     <row r="123">
@@ -5224,7 +5224,7 @@
         </is>
       </c>
       <c r="C126" s="19" t="n">
-        <v>1.150348</v>
+        <v>4.859173</v>
       </c>
     </row>
     <row r="127">
@@ -5365,19 +5365,19 @@
         <v>-0.01</v>
       </c>
       <c r="D140" s="25" t="n">
-        <v>1208.019471</v>
+        <v>31.456414</v>
       </c>
       <c r="E140" s="25" t="n">
-        <v>1093.370338</v>
+        <v>0</v>
       </c>
       <c r="F140" s="25" t="n">
-        <v>991.373831</v>
+        <v>0</v>
       </c>
       <c r="G140" s="25" t="n">
-        <v>900.045984</v>
+        <v>0</v>
       </c>
       <c r="H140" s="25" t="n">
-        <v>817.796476</v>
+        <v>0</v>
       </c>
     </row>
     <row r="141">
@@ -5385,19 +5385,19 @@
         <v>-0.005</v>
       </c>
       <c r="D141" s="25" t="n">
-        <v>1277.8744</v>
+        <v>60.811101</v>
       </c>
       <c r="E141" s="25" t="n">
-        <v>1152.840666</v>
+        <v>7.769302</v>
       </c>
       <c r="F141" s="25" t="n">
-        <v>1042.378781</v>
+        <v>0</v>
       </c>
       <c r="G141" s="25" t="n">
-        <v>944.079802</v>
+        <v>0</v>
       </c>
       <c r="H141" s="25" t="n">
-        <v>856.037547</v>
+        <v>0</v>
       </c>
     </row>
     <row r="142">
@@ -5405,19 +5405,19 @@
         <v>0</v>
       </c>
       <c r="D142" s="25" t="n">
-        <v>1357.581019</v>
+        <v>94.33722</v>
       </c>
       <c r="E142" s="25" t="n">
-        <v>1220.145672</v>
+        <v>36.05229</v>
       </c>
       <c r="F142" s="25" t="n">
-        <v>1099.687913</v>
+        <v>0</v>
       </c>
       <c r="G142" s="25" t="n">
-        <v>993.239402</v>
+        <v>0</v>
       </c>
       <c r="H142" s="25" t="n">
-        <v>898.4852529999999</v>
+        <v>0</v>
       </c>
     </row>
     <row r="143">
@@ -5425,19 +5425,19 @@
         <v>0.005</v>
       </c>
       <c r="D143" s="25" t="n">
-        <v>1449.381524</v>
+        <v>132.991952</v>
       </c>
       <c r="E143" s="25" t="n">
-        <v>1296.94275</v>
+        <v>68.354418</v>
       </c>
       <c r="F143" s="25" t="n">
-        <v>1164.547003</v>
+        <v>12.202781</v>
       </c>
       <c r="G143" s="25" t="n">
-        <v>1048.475099</v>
+        <v>0</v>
       </c>
       <c r="H143" s="25" t="n">
-        <v>945.874109</v>
+        <v>0</v>
       </c>
     </row>
     <row r="144">
@@ -5445,19 +5445,19 @@
         <v>0.01</v>
       </c>
       <c r="D144" s="25" t="n">
-        <v>1556.254384</v>
+        <v>178.049576</v>
       </c>
       <c r="E144" s="25" t="n">
-        <v>1385.39225</v>
+        <v>105.59792</v>
       </c>
       <c r="F144" s="25" t="n">
-        <v>1238.553218</v>
+        <v>43.330852</v>
       </c>
       <c r="G144" s="25" t="n">
-        <v>1110.9876</v>
+        <v>0</v>
       </c>
       <c r="H144" s="25" t="n">
-        <v>999.120199</v>
+        <v>0</v>
       </c>
     </row>
     <row r="146">
@@ -5494,19 +5494,19 @@
         <v>-0.02</v>
       </c>
       <c r="D148" s="25" t="n">
-        <v>369.496489</v>
+        <v>0</v>
       </c>
       <c r="E148" s="25" t="n">
-        <v>489.777155</v>
+        <v>0</v>
       </c>
       <c r="F148" s="25" t="n">
-        <v>620.757248</v>
+        <v>0</v>
       </c>
       <c r="G148" s="25" t="n">
-        <v>762.742266</v>
+        <v>0</v>
       </c>
       <c r="H148" s="25" t="n">
-        <v>915.907207</v>
+        <v>0</v>
       </c>
     </row>
     <row r="149">
@@ -5514,19 +5514,19 @@
         <v>-0.01</v>
       </c>
       <c r="D149" s="25" t="n">
-        <v>613.907031</v>
+        <v>0</v>
       </c>
       <c r="E149" s="25" t="n">
-        <v>769.445875</v>
+        <v>0</v>
       </c>
       <c r="F149" s="25" t="n">
-        <v>941.234788</v>
+        <v>0</v>
       </c>
       <c r="G149" s="25" t="n">
-        <v>1130.409352</v>
+        <v>0</v>
       </c>
       <c r="H149" s="25" t="n">
-        <v>1338.084867</v>
+        <v>0</v>
       </c>
     </row>
     <row r="150">
@@ -5534,19 +5534,19 @@
         <v>0</v>
       </c>
       <c r="D150" s="25" t="n">
-        <v>858.317573</v>
+        <v>0</v>
       </c>
       <c r="E150" s="25" t="n">
-        <v>1049.114595</v>
+        <v>0</v>
       </c>
       <c r="F150" s="25" t="n">
-        <v>1261.712327</v>
+        <v>0</v>
       </c>
       <c r="G150" s="25" t="n">
-        <v>1498.076438</v>
+        <v>24.929794</v>
       </c>
       <c r="H150" s="25" t="n">
-        <v>1760.262527</v>
+        <v>64.049369</v>
       </c>
     </row>
     <row r="151">
@@ -5554,19 +5554,19 @@
         <v>0.01</v>
       </c>
       <c r="D151" s="25" t="n">
-        <v>1102.728115</v>
+        <v>134.873759</v>
       </c>
       <c r="E151" s="25" t="n">
-        <v>1328.783315</v>
+        <v>217.104211</v>
       </c>
       <c r="F151" s="25" t="n">
-        <v>1582.189867</v>
+        <v>303.978149</v>
       </c>
       <c r="G151" s="25" t="n">
-        <v>1865.743524</v>
+        <v>394.883166</v>
       </c>
       <c r="H151" s="25" t="n">
-        <v>2182.440187</v>
+        <v>488.952751</v>
       </c>
     </row>
     <row r="152">
@@ -5574,19 +5574,19 @@
         <v>0.02</v>
       </c>
       <c r="D152" s="25" t="n">
-        <v>1347.138657</v>
+        <v>380.610285</v>
       </c>
       <c r="E152" s="25" t="n">
-        <v>1608.452036</v>
+        <v>498.367663</v>
       </c>
       <c r="F152" s="25" t="n">
-        <v>1902.667407</v>
+        <v>626.367928</v>
       </c>
       <c r="G152" s="25" t="n">
-        <v>2233.410609</v>
+        <v>764.836537</v>
       </c>
       <c r="H152" s="25" t="n">
-        <v>2604.617847</v>
+        <v>913.856133</v>
       </c>
     </row>
   </sheetData>
